--- a/data-manipulation-scripts/sheets-cleanup/sheets/ESPELHO FREIO - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ESPELHO FREIO - 29_01.xlsx
@@ -497,7 +497,9 @@
       <c r="C10" s="2">
         <v>1.0</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="2">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
